--- a/example/comparison.xlsx
+++ b/example/comparison.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,7 +447,13 @@
           <t>a2 -&gt; b2</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>=1+2 -&gt; =2+1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -460,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,6 +480,11 @@
           <t>Status</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Difference Sheet</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -483,9 +494,10 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>example/a.xlsx</t>
-        </is>
-      </c>
+          <t>.\example\a.xlsx</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -495,14 +507,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>example/b.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-    </row>
+          <t>.\example\b.xlsx</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -512,6 +522,11 @@
       <c r="B5" t="inlineStr">
         <is>
           <t>Differences found</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>df-Sheet1</t>
         </is>
       </c>
     </row>

--- a/example/comparison.xlsx
+++ b/example/comparison.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,13 @@
       <c r="B3" t="inlineStr">
         <is>
           <t>=1+2 -&gt; =2+1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>=1+1 -&gt; =2+1</t>
         </is>
       </c>
     </row>
@@ -494,7 +501,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>.\example\a.xlsx</t>
+          <t>example\a.xlsx</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -507,7 +514,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>.\example\b.xlsx</t>
+          <t>example\b.xlsx</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>

--- a/example/comparison.xlsx
+++ b/example/comparison.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,7 +447,20 @@
           <t>a2 -&gt; b2</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>=1+2 -&gt; =2+1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>=1+1 -&gt; =2+1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -460,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,6 +487,11 @@
           <t>Status</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Difference Sheet</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -483,9 +501,10 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>example/a.xlsx</t>
-        </is>
-      </c>
+          <t>example\a.xlsx</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -495,14 +514,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>example/b.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-    </row>
+          <t>example\b.xlsx</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -512,6 +529,11 @@
       <c r="B5" t="inlineStr">
         <is>
           <t>Differences found</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>df-Sheet1</t>
         </is>
       </c>
     </row>
